--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N60_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N60_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>3.110569970605747</v>
+        <v>0.5054676202234339</v>
       </c>
       <c r="D2" t="n">
-        <v>37.3206113675268</v>
+        <v>6.064599347223106</v>
       </c>
       <c r="E2" t="n">
-        <v>20.48339433468297</v>
+        <v>3.328551579385984</v>
       </c>
       <c r="F2" t="n">
-        <v>10.14078712038635</v>
+        <v>1.647877907062781</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>7.266024212156757</v>
+        <v>1.180728934475473</v>
       </c>
       <c r="D3" t="n">
-        <v>27.34270025382212</v>
+        <v>4.443188791246094</v>
       </c>
       <c r="E3" t="n">
-        <v>20.48339433468297</v>
+        <v>3.328551579385984</v>
       </c>
       <c r="F3" t="n">
-        <v>10.14078712038635</v>
+        <v>1.647877907062781</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>45.78900993454547</v>
+        <v>7.440714114363639</v>
       </c>
       <c r="D4" t="n">
-        <v>45.57994696130859</v>
+        <v>7.406741381212646</v>
       </c>
       <c r="E4" t="n">
-        <v>20.48339433468297</v>
+        <v>3.328551579385984</v>
       </c>
       <c r="F4" t="n">
-        <v>10.14078712038635</v>
+        <v>1.647877907062781</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>26.68567925578651</v>
+        <v>4.336422879065308</v>
       </c>
       <c r="D5" t="n">
-        <v>27.16940123131183</v>
+        <v>4.415027700088172</v>
       </c>
       <c r="E5" t="n">
-        <v>20.48339433468297</v>
+        <v>3.328551579385984</v>
       </c>
       <c r="F5" t="n">
-        <v>10.14078712038635</v>
+        <v>1.647877907062781</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>26.9667122960421</v>
+        <v>4.382090748106841</v>
       </c>
       <c r="D6" t="n">
-        <v>26.87739152945032</v>
+        <v>4.367576123535678</v>
       </c>
       <c r="E6" t="n">
-        <v>20.48339433468297</v>
+        <v>3.328551579385984</v>
       </c>
       <c r="F6" t="n">
-        <v>10.14078712038635</v>
+        <v>1.647877907062781</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>25.42175877859132</v>
+        <v>4.131035801521089</v>
       </c>
       <c r="D7" t="n">
-        <v>24.5623026372219</v>
+        <v>3.991374178548559</v>
       </c>
       <c r="E7" t="n">
-        <v>20.48339433468297</v>
+        <v>3.328551579385984</v>
       </c>
       <c r="F7" t="n">
-        <v>10.14078712038635</v>
+        <v>1.647877907062781</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>19.75413311368948</v>
+        <v>3.21004663097454</v>
       </c>
       <c r="D8" t="n">
-        <v>20.64205274689871</v>
+        <v>3.35433357137104</v>
       </c>
       <c r="E8" t="n">
-        <v>20.48339433468297</v>
+        <v>3.328551579385984</v>
       </c>
       <c r="F8" t="n">
-        <v>10.14078712038635</v>
+        <v>1.647877907062781</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>26.24839864899153</v>
+        <v>4.265364780461123</v>
       </c>
       <c r="D9" t="n">
-        <v>27.14098370264485</v>
+        <v>4.410409851679788</v>
       </c>
       <c r="E9" t="n">
-        <v>20.48339433468297</v>
+        <v>3.328551579385984</v>
       </c>
       <c r="F9" t="n">
-        <v>10.14078712038635</v>
+        <v>1.647877907062781</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>18.98114601055903</v>
+        <v>3.084436226715843</v>
       </c>
       <c r="D10" t="n">
-        <v>18.75323291915608</v>
+        <v>3.047400349362864</v>
       </c>
       <c r="E10" t="n">
-        <v>20.48339433468297</v>
+        <v>3.328551579385984</v>
       </c>
       <c r="F10" t="n">
-        <v>10.14078712038635</v>
+        <v>1.647877907062781</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>27.72720376996979</v>
+        <v>4.505670612620091</v>
       </c>
       <c r="D11" t="n">
-        <v>28.5927793132393</v>
+        <v>4.646326638401387</v>
       </c>
       <c r="E11" t="n">
-        <v>20.48339433468297</v>
+        <v>3.328551579385984</v>
       </c>
       <c r="F11" t="n">
-        <v>10.14078712038635</v>
+        <v>1.647877907062781</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>34.83715739980146</v>
+        <v>5.661038077467738</v>
       </c>
       <c r="D12" t="n">
-        <v>35.71305720588489</v>
+        <v>5.803371795956294</v>
       </c>
       <c r="E12" t="n">
-        <v>20.48339433468297</v>
+        <v>3.328551579385984</v>
       </c>
       <c r="F12" t="n">
-        <v>10.14078712038635</v>
+        <v>1.647877907062781</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>21.00213977893317</v>
+        <v>3.41284771407664</v>
       </c>
       <c r="D13" t="n">
-        <v>21.38451383427108</v>
+        <v>3.47498349806905</v>
       </c>
       <c r="E13" t="n">
-        <v>20.48339433468297</v>
+        <v>3.328551579385984</v>
       </c>
       <c r="F13" t="n">
-        <v>10.14078712038635</v>
+        <v>1.647877907062781</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>48.50061321403444</v>
+        <v>7.881349647280597</v>
       </c>
       <c r="D14" t="n">
-        <v>5.077381547038529</v>
+        <v>0.825074501393761</v>
       </c>
       <c r="E14" t="n">
-        <v>20.48339433468297</v>
+        <v>3.328551579385984</v>
       </c>
       <c r="F14" t="n">
-        <v>10.14078712038635</v>
+        <v>1.647877907062781</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>58.12042727596392</v>
+        <v>9.444569432344137</v>
       </c>
       <c r="D15" t="n">
-        <v>6.831754104719551</v>
+        <v>1.110160042016927</v>
       </c>
       <c r="E15" t="n">
-        <v>20.48339433468297</v>
+        <v>3.328551579385984</v>
       </c>
       <c r="F15" t="n">
-        <v>10.14078712038635</v>
+        <v>1.647877907062781</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>62.62197164751135</v>
+        <v>10.17607039272059</v>
       </c>
       <c r="D16" t="n">
-        <v>28.38722839808528</v>
+        <v>4.612924614688859</v>
       </c>
       <c r="E16" t="n">
-        <v>20.48339433468297</v>
+        <v>3.328551579385984</v>
       </c>
       <c r="F16" t="n">
-        <v>10.14078712038635</v>
+        <v>1.647877907062781</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>83.22992524181888</v>
+        <v>13.52486285179557</v>
       </c>
       <c r="D17" t="n">
-        <v>36.59737208139155</v>
+        <v>5.947072963226128</v>
       </c>
       <c r="E17" t="n">
-        <v>20.48339433468297</v>
+        <v>3.328551579385984</v>
       </c>
       <c r="F17" t="n">
-        <v>10.14078712038635</v>
+        <v>1.647877907062781</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
